--- a/data/raw/inventory/Week 24/Tonor/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 24/Tonor/Inventory Snapshot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 24\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D94B79-BCAB-4B79-871F-A30F400B3906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750A2661-0B72-4D09-A3C0-D7533A561E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="77">
   <si>
     <t>SKU</t>
   </si>
@@ -258,21 +258,23 @@
     <t>Pipeline</t>
   </si>
   <si>
-    <t>In-Transit Inventory</t>
-  </si>
-  <si>
     <t>Open Order</t>
+  </si>
+  <si>
+    <t>T30</t>
+  </si>
+  <si>
+    <t>TD310+</t>
+  </si>
+  <si>
+    <t>TC-2030</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,18 +313,6 @@
       <color theme="1"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111827"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -369,13 +359,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -395,42 +384,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Comma" xfId="3" builtinId="3"/>
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1953,103 +1913,88 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I47" s="9">
+      <c r="C47" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I47" s="1">
         <v>30</v>
       </c>
-      <c r="J47" s="7" t="s">
+      <c r="J47" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K47" s="8" t="s">
+    </row>
+    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I48" s="1">
+        <v>256</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I49" s="1">
+        <v>80</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I48" s="9">
-        <v>256</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I49" s="10">
-        <v>80</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A26:A44">
+    <cfRule type="duplicateValues" dxfId="9" priority="2165"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A35">
-    <cfRule type="duplicateValues" dxfId="11" priority="2133"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2134"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A49">
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2133"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="1894"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="7" priority="2105"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2105"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2106" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="5" priority="1892"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1893" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1892"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1893" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="3" priority="1890"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1891" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A47:A48">
-    <cfRule type="duplicateValues" dxfId="1" priority="2162"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A44">
-    <cfRule type="duplicateValues" dxfId="0" priority="2165"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1890"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1891" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
